--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sangram\Documents\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DDA7FBE-913F-4966-84E6-19497AFD3CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D92F199-705A-44FE-AC95-1EACE7BEC517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ADDFE7F9-2E9E-4277-BFB4-0EFB30AF740E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{ADDFE7F9-2E9E-4277-BFB4-0EFB30AF740E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -127,17 +130,103 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="8" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -601,6 +690,192 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D344506-DCB8-4FC9-8864-5D4769D7A936}">
+  <dimension ref="D3:K20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D3" s="5">
+        <v>46196</v>
+      </c>
+      <c r="K3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D4" s="5">
+        <v>46198</v>
+      </c>
+      <c r="K4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
+        <v>46186</v>
+      </c>
+      <c r="K5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D6" s="5">
+        <v>46196</v>
+      </c>
+      <c r="K6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D7" s="5">
+        <v>46195</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D8" s="5">
+        <v>46077</v>
+      </c>
+      <c r="K8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D9" s="5">
+        <v>46197</v>
+      </c>
+      <c r="K9">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="K11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="K13">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="E14" s="5">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="15" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="E15" s="5">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="16" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="E16" s="5">
+        <v>46186</v>
+      </c>
+      <c r="I16" s="5">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E17" s="5">
+        <v>46193</v>
+      </c>
+      <c r="I17" s="5">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="18" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E18" s="5">
+        <v>46196</v>
+      </c>
+      <c r="I18" s="5">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="19" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="I19" s="5">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="I20" s="5">
+        <v>46196</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D3:D7">
+    <cfRule type="expression" dxfId="11" priority="10">
+      <formula>D3=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="expression" dxfId="10" priority="9">
+      <formula>D8=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K13">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThanOrEqual">
+      <formula>K3&lt;50</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThanOrEqual">
+      <formula>K3&lt;50</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>K3&lt;50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:E18">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>E14=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16:I20">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>I16Today()</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>I16=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85074514-E146-4683-AC4A-030E9FCA6434}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA9B2E3-9801-4DAF-A44B-451248CB7AE7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D265E26-D102-413A-A560-C81E287AA03E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
